--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488081_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488081_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1413</v>
+        <v>13.6144</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1598</v>
+        <v>13.324</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0185</v>
+        <v>0.2904</v>
       </c>
       <c r="G2" t="n">
         <v>10.6608</v>
@@ -610,13 +610,13 @@
         <v>0.9911</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0547</v>
+        <v>0.4184</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1176</v>
+        <v>0.2818</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1723</v>
+        <v>0.1366</v>
       </c>
       <c r="V2" t="n">
         <v>1.5441</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1843</v>
+        <v>2.716</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1662</v>
+        <v>2.716</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0181</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3938</v>
+        <v>2.716</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2313</v>
+        <v>0.908</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1625</v>
+        <v>1.808</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2341</v>
+        <v>2.716</v>
       </c>
       <c r="K3" t="n">
-        <v>3.632</v>
+        <v>0.908</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3979</v>
+        <v>1.808</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8403</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4007</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5604</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.784</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1186</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7093</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4093</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5441</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>D. GARCIA GAZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.716</v>
+        <v>1.2506</v>
       </c>
       <c r="E4" t="n">
-        <v>2.716</v>
+        <v>1.8957</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.6451</v>
       </c>
       <c r="G4" t="n">
-        <v>2.716</v>
+        <v>-0.9022</v>
       </c>
       <c r="H4" t="n">
-        <v>0.908</v>
+        <v>-0.6707</v>
       </c>
       <c r="I4" t="n">
-        <v>1.808</v>
+        <v>-0.2315</v>
       </c>
       <c r="J4" t="n">
-        <v>2.716</v>
+        <v>1.0771</v>
       </c>
       <c r="K4" t="n">
-        <v>0.908</v>
+        <v>1.4672</v>
       </c>
       <c r="L4" t="n">
-        <v>1.808</v>
+        <v>-0.3901</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.9793</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.1379</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.1586</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.4543</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.0255</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.4798</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.2843</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.8175</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GARCIA GAZQUEZ</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.528</v>
+        <v>0.7744</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4258</v>
+        <v>1.5987</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8978</v>
+        <v>-0.8243</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9022</v>
+        <v>2.3938</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6707</v>
+        <v>2.2313</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2315</v>
+        <v>0.1625</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0771</v>
+        <v>3.2341</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4672</v>
+        <v>3.632</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3901</v>
+        <v>-0.3979</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9793</v>
+        <v>-0.8403</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1379</v>
+        <v>-1.4007</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1586</v>
+        <v>0.5604</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5858</v>
+        <v>-1.784</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2683</v>
+        <v>1.7087</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4954</v>
+        <v>1.1418</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2271</v>
+        <v>0.5669</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2843</v>
+        <v>-1.5441</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8175</v>
+        <v>0.1962</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5331</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.031</v>
+        <v>0.3925</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3316</v>
+        <v>-0.1021</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.3006</v>
+        <v>0.4946</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1615</v>
+        <v>1.1844</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9327</v>
+        <v>1.0315</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7712</v>
+        <v>0.1529</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6912</v>
+        <v>1.7473</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8676</v>
+        <v>2.0247</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8236</v>
+        <v>-0.2774</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8527</v>
+        <v>-0.5629</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8003</v>
+        <v>-0.9932</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0524</v>
+        <v>0.4303</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5858</v>
+        <v>-1.784</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>0.347</v>
+        <v>0.122</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4333</v>
+        <v>-0.0128</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0864</v>
+        <v>0.1347</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7403</v>
+        <v>0.8701</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.9474</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1345</v>
+        <v>0.3109</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7133</v>
+        <v>4.1903</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5788</v>
+        <v>-3.8794</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1844</v>
+        <v>-0.1615</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0315</v>
+        <v>-0.9327</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1529</v>
+        <v>0.7712</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7473</v>
+        <v>2.6912</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0247</v>
+        <v>0.8676</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2774</v>
+        <v>1.8236</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5629</v>
+        <v>-2.8527</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9932</v>
+        <v>-1.8003</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4303</v>
+        <v>-1.0524</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.405</v>
+        <v>0.6268</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.624</v>
+        <v>0.292</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2189</v>
+        <v>0.3348</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8701</v>
+        <v>-1.7403</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6278</v>
+        <v>-2.0915</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0885</v>
+        <v>-0.496</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5393</v>
+        <v>-1.5955</v>
       </c>
       <c r="G8" t="n">
         <v>-1.312</v>
@@ -1078,13 +1078,13 @@
         <v>0.3964</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4948</v>
+        <v>0.0312</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4295</v>
+        <v>0.0221</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0653</v>
+        <v>0.0091</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8877</v>
+        <v>-2.4248</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2415</v>
+        <v>-1.1604</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6463</v>
+        <v>-1.2644</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0521</v>
+        <v>-1.5393</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0148</v>
+        <v>-2.4252</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0669</v>
+        <v>0.886</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0081</v>
+        <v>-0.3653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08069999999999999</v>
+        <v>-0.8267</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0726</v>
+        <v>0.4614</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0602</v>
+        <v>-1.1739</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.066</v>
+        <v>-1.5985</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0057</v>
+        <v>0.4246</v>
       </c>
       <c r="P9" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6196</v>
+        <v>-0.5506</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2496</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.37</v>
+        <v>-0.4801</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4142</v>
+        <v>-0.5331</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4142</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4883</v>
+        <v>-2.6278</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1396</v>
+        <v>-0.0377</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3487</v>
+        <v>-2.5901</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5393</v>
+        <v>-0.0521</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4252</v>
+        <v>0.0148</v>
       </c>
       <c r="I10" t="n">
-        <v>0.886</v>
+        <v>-0.0669</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3653</v>
+        <v>0.0081</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8267</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4614</v>
+        <v>-0.0726</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1739</v>
+        <v>-0.0602</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5985</v>
+        <v>-0.066</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4246</v>
+        <v>0.0057</v>
       </c>
       <c r="P10" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6141</v>
+        <v>-0.3597</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0497</v>
+        <v>-0.0459</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5644</v>
+        <v>-0.3139</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5331</v>
+        <v>-2.4142</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7997</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5782</v>
+        <v>-3.7153</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5412</v>
+        <v>-2.8468</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.037</v>
+        <v>-0.8685</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4939</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0931</v>
+        <v>-0.2303</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7453</v>
+        <v>0.4397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8385</v>
+        <v>-0.67</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.006</v>
+        <v>-4.0093</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1524</v>
+        <v>0.1532</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8536</v>
+        <v>-4.1625</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1288</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0216</v>
+        <v>0.0184</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6753</v>
+        <v>-0.3697</v>
       </c>
       <c r="U12" t="n">
-        <v>0.697</v>
+        <v>0.3881</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6917</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.878099999999997</v>
+        <v>4.190100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>18.9229</v>
+        <v>19.2349</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.0449</v>
+        <v>-15.0448</v>
       </c>
       <c r="G13" t="n">
         <v>9.3652</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6792000000000011</v>
+        <v>0.6792000000000005</v>
       </c>
       <c r="I13" t="n">
-        <v>8.686099999999998</v>
+        <v>8.6861</v>
       </c>
       <c r="J13" t="n">
         <v>20.8445</v>
@@ -1465,16 +1465,16 @@
         <v>-11.8932</v>
       </c>
       <c r="R13" t="n">
-        <v>9.910999999999998</v>
+        <v>9.911</v>
       </c>
       <c r="S13" t="n">
-        <v>1.927199999999999</v>
+        <v>2.2392</v>
       </c>
       <c r="T13" t="n">
-        <v>1.340999999999999</v>
+        <v>1.653</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5860000000000002</v>
+        <v>0.5859999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-5.432</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7478</v>
+        <v>3.627</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8816</v>
+        <v>4.3723</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1338</v>
+        <v>-0.7453</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0755</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0988</v>
+        <v>-0.022</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6647</v>
+        <v>0.1553</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5658</v>
+        <v>-0.1773</v>
       </c>
       <c r="V14" t="n">
         <v>5.7156</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7378</v>
+        <v>1.0798</v>
       </c>
       <c r="E15" t="n">
-        <v>5.212</v>
+        <v>3.5821</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4742</v>
+        <v>-2.5023</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1308</v>
@@ -1624,13 +1624,13 @@
         <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>0.592</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3973</v>
+        <v>0.7674</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1473</v>
+        <v>-0.1754</v>
       </c>
       <c r="V15" t="n">
         <v>1.4204</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1897</v>
+        <v>0.9683</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9438</v>
+        <v>1.6382</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7541</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.3126</v>
@@ -1702,13 +1702,13 @@
         <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>0.214</v>
+        <v>-0.0073</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3671</v>
+        <v>0.0615</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1531</v>
+        <v>-0.0689</v>
       </c>
       <c r="V16" t="n">
         <v>0.2666</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7617</v>
+        <v>0.8061</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6308</v>
+        <v>0.427</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1309</v>
+        <v>0.3791</v>
       </c>
       <c r="G17" t="n">
         <v>1.0298</v>
@@ -1780,13 +1780,13 @@
         <v>0.1982</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1373</v>
+        <v>0.1817</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4295</v>
+        <v>0.2258</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2923</v>
+        <v>-0.0441</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6036</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0228</v>
+        <v>0.3845</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1385</v>
+        <v>0.4442</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1158</v>
+        <v>-0.0596</v>
       </c>
       <c r="G18" t="n">
         <v>-0.406</v>
@@ -1858,13 +1858,13 @@
         <v>0.3964</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2342</v>
+        <v>0.1276</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1762</v>
+        <v>0.1294</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0581</v>
+        <v>-0.0019</v>
       </c>
       <c r="V18" t="n">
         <v>0.2666</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5342</v>
+        <v>0.1286</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6329</v>
+        <v>4.2441</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.1671</v>
+        <v>-4.1155</v>
       </c>
       <c r="G19" t="n">
         <v>2.2149</v>
@@ -1936,13 +1936,13 @@
         <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5392</v>
+        <v>-0.8764</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2993</v>
+        <v>-0.6881</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2399</v>
+        <v>-0.1883</v>
       </c>
       <c r="V19" t="n">
         <v>-2.201</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6253</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3202</v>
+        <v>3.1352</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9455</v>
+        <v>-3.2028</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1665</v>
@@ -2014,13 +2014,13 @@
         <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1212</v>
+        <v>-0.5635</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4351</v>
+        <v>-0.6202</v>
       </c>
       <c r="U20" t="n">
-        <v>0.314</v>
+        <v>0.0567</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3199</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7359</v>
+        <v>-1.2207</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5683</v>
+        <v>-0.1608</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1676</v>
+        <v>-1.0599</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5733</v>
@@ -2092,13 +2092,13 @@
         <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2925</v>
+        <v>-0.7773</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1855</v>
+        <v>-0.7781</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.107</v>
+        <v>0.0008</v>
       </c>
       <c r="V21" t="n">
         <v>0.337</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7387</v>
+        <v>-1.851</v>
       </c>
       <c r="E22" t="n">
         <v>0.7474</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4861</v>
+        <v>-2.5984</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4182</v>
@@ -2170,13 +2170,13 @@
         <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0609</v>
+        <v>-0.0514</v>
       </c>
       <c r="T22" t="n">
         <v>-0.121</v>
       </c>
       <c r="U22" t="n">
-        <v>0.182</v>
+        <v>0.0696</v>
       </c>
       <c r="V22" t="n">
         <v>2.0239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8765</v>
+        <v>-2.7923</v>
       </c>
       <c r="E23" t="n">
         <v>-0.8594000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0172</v>
+        <v>-1.9329</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8108</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2045</v>
+        <v>-0.1202</v>
       </c>
       <c r="T23" t="n">
         <v>0.011</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8701</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8274</v>
+        <v>-4.2619</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.035</v>
+        <v>-2.5256</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7924</v>
+        <v>-1.7362</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3414</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2966</v>
+        <v>0.2689</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2386</v>
+        <v>0.2708</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0581</v>
+        <v>-0.0019</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6036</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.878200000000001</v>
+        <v>-3.1992</v>
       </c>
       <c r="E25" t="n">
-        <v>15.0445</v>
+        <v>15.0447</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.9229</v>
+        <v>-18.2437</v>
       </c>
       <c r="G25" t="n">
         <v>-9.3652</v>
@@ -2404,13 +2404,13 @@
         <v>11.8931</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9272</v>
+        <v>-1.2479</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5860999999999998</v>
+        <v>-0.5861999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3411</v>
+        <v>-0.662</v>
       </c>
       <c r="V25" t="n">
         <v>5.4319</v>
